--- a/DanhSachDaiBieu_Mau.xlsx
+++ b/DanhSachDaiBieu_Mau.xlsx
@@ -1,47 +1,980 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mongvanmuoi/Documents/ANTIGRAVITY IDE CODE/HỆ THỐNG ĐIỂM DANH QR/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F79EC3A-6608-E548-AA0B-4C73F02BC3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="20800" yWindow="5200" windowWidth="20160" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="312">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>Đơn vị</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Đinh Khắc Yên</t>
+  </si>
+  <si>
+    <t>Ủy viên Ban Chấp hành</t>
+  </si>
+  <si>
+    <t>'0949192888</t>
+  </si>
+  <si>
+    <t>Nguyễn Duy Hiếu</t>
+  </si>
+  <si>
+    <t>'0888929456</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hải</t>
+  </si>
+  <si>
+    <t>'0986609380</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mai Hương</t>
+  </si>
+  <si>
+    <t>'0916712666</t>
+  </si>
+  <si>
+    <t>Tăng Kết Dư</t>
+  </si>
+  <si>
+    <t>'0945754838</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mai Thức</t>
+  </si>
+  <si>
+    <t>'0984849379</t>
+  </si>
+  <si>
+    <t>Sầm Văn Thượng</t>
+  </si>
+  <si>
+    <t>'0914778099</t>
+  </si>
+  <si>
+    <t>Trần Thị Khang</t>
+  </si>
+  <si>
+    <t>'0983233084</t>
+  </si>
+  <si>
+    <t>Lý Đạt Lam</t>
+  </si>
+  <si>
+    <t>'0911793666</t>
+  </si>
+  <si>
+    <t>Nguyễn Trung Kiên</t>
+  </si>
+  <si>
+    <t>'09122073307</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thu Huyền</t>
+  </si>
+  <si>
+    <t>'0832108282</t>
+  </si>
+  <si>
+    <t>Hoàng Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>'0912234342</t>
+  </si>
+  <si>
+    <t>Trần Nguyên Thủ</t>
+  </si>
+  <si>
+    <t>'0889698966</t>
+  </si>
+  <si>
+    <t>Nguyễn Viết Giang</t>
+  </si>
+  <si>
+    <t>'0919684164</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Yên</t>
+  </si>
+  <si>
+    <t>'0986658286</t>
+  </si>
+  <si>
+    <t>Lã Văn Quảng</t>
+  </si>
+  <si>
+    <t>'0384156667</t>
+  </si>
+  <si>
+    <t>Phùng Thị Thu Hương</t>
+  </si>
+  <si>
+    <t>'0989216673</t>
+  </si>
+  <si>
+    <t>Trần Thị Lợi</t>
+  </si>
+  <si>
+    <t>'0942375018</t>
+  </si>
+  <si>
+    <t>Đàm Thị Kim Nhung</t>
+  </si>
+  <si>
+    <t>'0983625919</t>
+  </si>
+  <si>
+    <t>Phạm Văn Tình</t>
+  </si>
+  <si>
+    <t>'0385987518</t>
+  </si>
+  <si>
+    <t>Vũ Tuấn Anh</t>
+  </si>
+  <si>
+    <t>'0888141828</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hương</t>
+  </si>
+  <si>
+    <t>Cần bổ sung</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Tuân</t>
+  </si>
+  <si>
+    <t>'0968515964</t>
+  </si>
+  <si>
+    <t>Lê Thị Quỳnh</t>
+  </si>
+  <si>
+    <t>'0979910646</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>'0354078668</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thư</t>
+  </si>
+  <si>
+    <t>'0915454019</t>
+  </si>
+  <si>
+    <t>Trần Trung Thành</t>
+  </si>
+  <si>
+    <t>'0912101103</t>
+  </si>
+  <si>
+    <t>Hoàng Quốc Đạt</t>
+  </si>
+  <si>
+    <t>'0787035812</t>
+  </si>
+  <si>
+    <t>Triệu Văn Chín</t>
+  </si>
+  <si>
+    <t>'0974763351</t>
+  </si>
+  <si>
+    <t>Phùng Văn Nâng</t>
+  </si>
+  <si>
+    <t>'0974818926</t>
+  </si>
+  <si>
+    <t>Mông Việt Cành</t>
+  </si>
+  <si>
+    <t>'0972113557</t>
+  </si>
+  <si>
+    <t>Đỗ Trần Thu Thảo</t>
+  </si>
+  <si>
+    <t>Ủy viên Ủy ban Kiểm tra Đảng ủy</t>
+  </si>
+  <si>
+    <t>Lê Thị Hương</t>
+  </si>
+  <si>
+    <t>Tăng Văn Thập</t>
+  </si>
+  <si>
+    <t>Lô Văn Hùng</t>
+  </si>
+  <si>
+    <t>Ban Quản lý dự án</t>
+  </si>
+  <si>
+    <t>Đỗ Trung Nguyên</t>
+  </si>
+  <si>
+    <t>Bùi Mạnh Linh</t>
+  </si>
+  <si>
+    <t>Văn phòng đăng ký đất đai</t>
+  </si>
+  <si>
+    <t>'0945234000</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Thanh Thủy</t>
+  </si>
+  <si>
+    <t>Trung tâm Dịch vụ Hành Chính công xã</t>
+  </si>
+  <si>
+    <t>0972446399</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Thắng</t>
+  </si>
+  <si>
+    <t>Trung tâm Dịch vụ Tổng hợp xã</t>
+  </si>
+  <si>
+    <t>'0949043097</t>
+  </si>
+  <si>
+    <t>Phạm Thị Thúy</t>
+  </si>
+  <si>
+    <t>Phòng Nông nghiệp và Môi trường</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hà</t>
+  </si>
+  <si>
+    <t>Phòng Văn hóa - Xã hội</t>
+  </si>
+  <si>
+    <t>Trịnh Thị Ngoạn</t>
+  </si>
+  <si>
+    <t>Trường Mầm non Hoa Huệ</t>
+  </si>
+  <si>
+    <t>'0858570289</t>
+  </si>
+  <si>
+    <t>Hoàng Liên Ngân</t>
+  </si>
+  <si>
+    <t>Trường Mầm non Hồng Ngọc</t>
+  </si>
+  <si>
+    <t>'0396266214</t>
+  </si>
+  <si>
+    <t>Vũ Minh Hải</t>
+  </si>
+  <si>
+    <t>Trường Mầm non Hoa Phượng</t>
+  </si>
+  <si>
+    <t>'0945908672</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thanh</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Trần Phú</t>
+  </si>
+  <si>
+    <t>'0949679068</t>
+  </si>
+  <si>
+    <t>Nguyễn Vũ Nam</t>
+  </si>
+  <si>
+    <t>Trường TH&amp;THCS Yên Thắng</t>
+  </si>
+  <si>
+    <t>'0986194154</t>
+  </si>
+  <si>
+    <t>Đinh Hữu Khánh</t>
+  </si>
+  <si>
+    <t>Trường THCS Lê Hồng Phong</t>
+  </si>
+  <si>
+    <t>'0978514377</t>
+  </si>
+  <si>
+    <t>Vũ Thanh Sơn</t>
+  </si>
+  <si>
+    <t>Trường THCS Nguyễn Thái Học</t>
+  </si>
+  <si>
+    <t>'0918598955</t>
+  </si>
+  <si>
+    <t>Đỗ Đức Quân</t>
+  </si>
+  <si>
+    <t>Trường PTDTNT - THCS</t>
+  </si>
+  <si>
+    <t>'0914643680</t>
+  </si>
+  <si>
+    <t>Mông Thanh Dũng</t>
+  </si>
+  <si>
+    <t>Trung tâm GDNN - GDTX</t>
+  </si>
+  <si>
+    <t>Hoàng Anh Tuấn</t>
+  </si>
+  <si>
+    <t>TTYT khu vực Lục Yên</t>
+  </si>
+  <si>
+    <t>Triệu Văn Đức</t>
+  </si>
+  <si>
+    <t>Công an xã</t>
+  </si>
+  <si>
+    <t>'0835936333</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Doanh</t>
+  </si>
+  <si>
+    <t>Triệu Thị Na</t>
+  </si>
+  <si>
+    <t>'0944211267</t>
+  </si>
+  <si>
+    <t>Vũ Bằng Giang</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Minh Xuân</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Biên Thùy</t>
+  </si>
+  <si>
+    <t>Đỗ Xuân Đạt</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Vở</t>
+  </si>
+  <si>
+    <t>'0395509676</t>
+  </si>
+  <si>
+    <t>Lê Thị Ánh Hồng</t>
+  </si>
+  <si>
+    <t>Đinh Văn Năm</t>
+  </si>
+  <si>
+    <t>Phạm Thanh Sơn</t>
+  </si>
+  <si>
+    <t>Tạ Thị Dung</t>
+  </si>
+  <si>
+    <t>Vi Thị Kim Thảo</t>
+  </si>
+  <si>
+    <t>Trường TH&amp;THCS Liễu Đô</t>
+  </si>
+  <si>
+    <t>Trần Xuân Hữu</t>
+  </si>
+  <si>
+    <t>Trường PTTH Hoàng Văn Thụ</t>
+  </si>
+  <si>
+    <t>Vy Thị Lý</t>
+  </si>
+  <si>
+    <t>Trạm y tế Lục Yên</t>
+  </si>
+  <si>
+    <t>Đỗ Xuân Phùng</t>
+  </si>
+  <si>
+    <t>Công ty TNHH Lục Yên</t>
+  </si>
+  <si>
+    <t>'0966332193</t>
+  </si>
+  <si>
+    <t>Trương Ngân Linh</t>
+  </si>
+  <si>
+    <t>Vi Quốc Tuấn</t>
+  </si>
+  <si>
+    <t>Công ty TNHH Lâm Hoàng</t>
+  </si>
+  <si>
+    <t>Hà Minh Tuấn</t>
+  </si>
+  <si>
+    <t>Điện lực Lục Yên</t>
+  </si>
+  <si>
+    <t>Trần Khắc Đức</t>
+  </si>
+  <si>
+    <t>Hoàng Quốc Dũng</t>
+  </si>
+  <si>
+    <t>Bưu điện Văn Yên - Lục Yên</t>
+  </si>
+  <si>
+    <t>Trần Thu Hà</t>
+  </si>
+  <si>
+    <t>Dương Quốc Tuấn</t>
+  </si>
+  <si>
+    <t>Phòng Giao dịch NHCS xã hội Lục Yên</t>
+  </si>
+  <si>
+    <t>Nông Ngọc Huấn</t>
+  </si>
+  <si>
+    <t>Hà Tiến Công</t>
+  </si>
+  <si>
+    <t>Hạt Kiểm lâm khu vực Lục Yên</t>
+  </si>
+  <si>
+    <t>Lương Ngọc Sơn</t>
+  </si>
+  <si>
+    <t>Lại Đức Tính</t>
+  </si>
+  <si>
+    <t>VNPT Lục Yên</t>
+  </si>
+  <si>
+    <t>Trần Đức Hiếu</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Nhung</t>
+  </si>
+  <si>
+    <t>Thôn 1</t>
+  </si>
+  <si>
+    <t>0836002268</t>
+  </si>
+  <si>
+    <t>Lê Thị Hồng</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Chọn</t>
+  </si>
+  <si>
+    <t>'0869979565</t>
+  </si>
+  <si>
+    <t>Lý Thị Trao</t>
+  </si>
+  <si>
+    <t>Thôn 2</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Xuyến</t>
+  </si>
+  <si>
+    <t>'0856856485</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Tuyết</t>
+  </si>
+  <si>
+    <t>Thôn 3</t>
+  </si>
+  <si>
+    <t>'0987419548</t>
+  </si>
+  <si>
+    <t>Phạm Văn Cường</t>
+  </si>
+  <si>
+    <t>'0388478573</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Giang Anh</t>
+  </si>
+  <si>
+    <t>Thôn 4</t>
+  </si>
+  <si>
+    <t>'0984954743</t>
+  </si>
+  <si>
+    <t>Phạm Việt Hùng</t>
+  </si>
+  <si>
+    <t>'0979584180</t>
+  </si>
+  <si>
+    <t>Vũ Cao Khiếu</t>
+  </si>
+  <si>
+    <t>Thôn 5</t>
+  </si>
+  <si>
+    <t>'0912508257</t>
+  </si>
+  <si>
+    <t>Đỗ Ngọc Thuật</t>
+  </si>
+  <si>
+    <t>'0974767159</t>
+  </si>
+  <si>
+    <t>Lê Thị Kim Tuyến</t>
+  </si>
+  <si>
+    <t>Thôn 6</t>
+  </si>
+  <si>
+    <t>'0912354215</t>
+  </si>
+  <si>
+    <t>Triệu Thị Diện</t>
+  </si>
+  <si>
+    <t>Thôn 7</t>
+  </si>
+  <si>
+    <t>'0975706637</t>
+  </si>
+  <si>
+    <t>Nông Thị Tài</t>
+  </si>
+  <si>
+    <t>Thôn 8</t>
+  </si>
+  <si>
+    <t>'0388099233</t>
+  </si>
+  <si>
+    <t>Phạm Thị Khang</t>
+  </si>
+  <si>
+    <t>'0379799306</t>
+  </si>
+  <si>
+    <t>Lương Thị Hương</t>
+  </si>
+  <si>
+    <t>Thôn 9</t>
+  </si>
+  <si>
+    <t>'0985316499</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Toán</t>
+  </si>
+  <si>
+    <t>'0919494827</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Hùng</t>
+  </si>
+  <si>
+    <t>Thôn 10</t>
+  </si>
+  <si>
+    <t>'0961613595</t>
+  </si>
+  <si>
+    <t>Lý Văn Chúng</t>
+  </si>
+  <si>
+    <t>Thôn 11</t>
+  </si>
+  <si>
+    <t>'0914557486</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Mến</t>
+  </si>
+  <si>
+    <t>'0398704665</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Khóa</t>
+  </si>
+  <si>
+    <t>Thôn 12</t>
+  </si>
+  <si>
+    <t>Tăng Văn Toàn</t>
+  </si>
+  <si>
+    <t>'0982527455</t>
+  </si>
+  <si>
+    <t>Mông Sơn</t>
+  </si>
+  <si>
+    <t>Thôn 13</t>
+  </si>
+  <si>
+    <t>'0336640848</t>
+  </si>
+  <si>
+    <t>Hoàng Ngọc Tính</t>
+  </si>
+  <si>
+    <t>'0916282964</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Ước</t>
+  </si>
+  <si>
+    <t>Đồng Thanh</t>
+  </si>
+  <si>
+    <t>'0766136386</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Đoàn</t>
+  </si>
+  <si>
+    <t>'0398916918</t>
+  </si>
+  <si>
+    <t>Lại Thị Hồng Phượng</t>
+  </si>
+  <si>
+    <t>Cây Thị</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Huy</t>
+  </si>
+  <si>
+    <t>'0347135844</t>
+  </si>
+  <si>
+    <t>Hoàng Kim Quê</t>
+  </si>
+  <si>
+    <t>'0986991043</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nghiệp</t>
+  </si>
+  <si>
+    <t>Chính Quân</t>
+  </si>
+  <si>
+    <t>'0345691966</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Lưỡng</t>
+  </si>
+  <si>
+    <t>'0379284895</t>
+  </si>
+  <si>
+    <t>Nhạc Văn Phì</t>
+  </si>
+  <si>
+    <t>'0982702508</t>
+  </si>
+  <si>
+    <t>Vương Thị Chở</t>
+  </si>
+  <si>
+    <t>Làng Tàu</t>
+  </si>
+  <si>
+    <t>'0374672622</t>
+  </si>
+  <si>
+    <t>Phan Duy Đạt</t>
+  </si>
+  <si>
+    <t>'0987685919</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hồng Duyên</t>
+  </si>
+  <si>
+    <t>Nguyễn Quang Tảo</t>
+  </si>
+  <si>
+    <t>Nà Khà</t>
+  </si>
+  <si>
+    <t>'0383622667</t>
+  </si>
+  <si>
+    <t>Nguyễn Quang Sông</t>
+  </si>
+  <si>
+    <t>'0979985832</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Thứ</t>
+  </si>
+  <si>
+    <t>Loong Tra</t>
+  </si>
+  <si>
+    <t>'0984320398</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Trà</t>
+  </si>
+  <si>
+    <t>Kéo Quạng</t>
+  </si>
+  <si>
+    <t>'0328443501</t>
+  </si>
+  <si>
+    <t>Hoàng Quốc Khánh</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Sách</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Phố</t>
+  </si>
+  <si>
+    <t>Nà Vài</t>
+  </si>
+  <si>
+    <t>'0378396907</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Sinh</t>
+  </si>
+  <si>
+    <t>Hoàng Đình Chiến</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Tình</t>
+  </si>
+  <si>
+    <t>Xuân Yên</t>
+  </si>
+  <si>
+    <t>'0383906734</t>
+  </si>
+  <si>
+    <t>Hoàng Ngọc Thắng</t>
+  </si>
+  <si>
+    <t>Vương Ngọc Đồn</t>
+  </si>
+  <si>
+    <t>Tông Cụm</t>
+  </si>
+  <si>
+    <t>'0376347009</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Tuyến</t>
+  </si>
+  <si>
+    <t>'0376234134</t>
+  </si>
+  <si>
+    <t>Lộc Văn Hồng</t>
+  </si>
+  <si>
+    <t>Trang Thành</t>
+  </si>
+  <si>
+    <t>'0984882706</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Ninh</t>
+  </si>
+  <si>
+    <t>'0332572956</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Đạo</t>
+  </si>
+  <si>
+    <t>Trần Phú</t>
+  </si>
+  <si>
+    <t>'0989396204</t>
+  </si>
+  <si>
+    <t>Phạm Quang Luận</t>
+  </si>
+  <si>
+    <t>Vương Văn Biện</t>
+  </si>
+  <si>
+    <t>Át Thượng</t>
+  </si>
+  <si>
+    <t>'0986211308</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Đàn</t>
+  </si>
+  <si>
+    <t>'0965744686</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Quế</t>
+  </si>
+  <si>
+    <t>'0987691869</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Ổn</t>
+  </si>
+  <si>
+    <t>Làng Phạ</t>
+  </si>
+  <si>
+    <t>'0333036253</t>
+  </si>
+  <si>
+    <t>Mông Văn Tiềm</t>
+  </si>
+  <si>
+    <t>'0975706426</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Thòng</t>
+  </si>
+  <si>
+    <t>Đồng Cáy</t>
+  </si>
+  <si>
+    <t>'0385968144</t>
+  </si>
+  <si>
+    <t>Lương Thị Thân</t>
+  </si>
+  <si>
+    <t>'0369129309</t>
+  </si>
+  <si>
+    <t>Mông Thị Long Biên</t>
+  </si>
+  <si>
+    <t>Thâm Pồng</t>
+  </si>
+  <si>
+    <t>'0972950478</t>
+  </si>
+  <si>
+    <t>Hoàng Anh Tuyên</t>
+  </si>
+  <si>
+    <t>'0386810504</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Hợp</t>
+  </si>
+  <si>
+    <t>Nà Khao</t>
+  </si>
+  <si>
+    <t>'0366758163</t>
+  </si>
+  <si>
+    <t>Nguyễn Bình Lực</t>
+  </si>
+  <si>
+    <t>'0989928165</t>
+  </si>
+  <si>
+    <t>Phùng Quốc Trường</t>
+  </si>
+  <si>
+    <t>Làng Thọc</t>
+  </si>
+  <si>
+    <t>'0378200019</t>
+  </si>
+  <si>
+    <t>Hoàng Xuân Thu</t>
+  </si>
+  <si>
+    <t>'0915516919</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Minh</t>
+  </si>
+  <si>
+    <t>'0386810558</t>
+  </si>
+  <si>
+    <t>Mông Thị Kỳ</t>
+  </si>
+  <si>
+    <t>'0366931846</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,14 +997,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,26 +1369,3877 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D597"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>STT</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Họ và tên</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Đơn vị</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Số điện thoại</v>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="6"/>
+      <c r="D148" s="7"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="6"/>
+      <c r="D149" s="7"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="6"/>
+      <c r="D150" s="7"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="6"/>
+      <c r="D151" s="7"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="6"/>
+      <c r="D152" s="7"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="6"/>
+      <c r="D153" s="7"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="6"/>
+      <c r="D154" s="7"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="6"/>
+      <c r="D155" s="7"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="6"/>
+      <c r="D156" s="7"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="6"/>
+      <c r="D157" s="7"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="6"/>
+      <c r="D158" s="7"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" s="6"/>
+      <c r="D159" s="7"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" s="6"/>
+      <c r="D160" s="7"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" s="6"/>
+      <c r="D161" s="7"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="6"/>
+      <c r="D162" s="7"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="6"/>
+      <c r="D163" s="7"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="6"/>
+      <c r="D164" s="7"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" s="6"/>
+      <c r="D165" s="7"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="6"/>
+      <c r="D166" s="7"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="6"/>
+      <c r="D167" s="7"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="6"/>
+      <c r="D168" s="7"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="6"/>
+      <c r="D169" s="7"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="6"/>
+      <c r="D170" s="7"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="6"/>
+      <c r="D171" s="7"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="6"/>
+      <c r="D172" s="7"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="6"/>
+      <c r="D173" s="7"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="6"/>
+      <c r="D174" s="7"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="6"/>
+      <c r="D175" s="7"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="6"/>
+      <c r="D176" s="7"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="6"/>
+      <c r="D177" s="7"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="6"/>
+      <c r="D178" s="7"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="6"/>
+      <c r="D179" s="7"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" s="6"/>
+      <c r="D180" s="7"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="6"/>
+      <c r="D181" s="7"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="6"/>
+      <c r="D182" s="7"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" s="6"/>
+      <c r="D183" s="7"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" s="6"/>
+      <c r="D184" s="7"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" s="6"/>
+      <c r="D185" s="7"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" s="6"/>
+      <c r="D186" s="7"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" s="6"/>
+      <c r="D187" s="7"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" s="6"/>
+      <c r="D188" s="7"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" s="6"/>
+      <c r="D189" s="7"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" s="6"/>
+      <c r="D190" s="7"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" s="6"/>
+      <c r="D191" s="7"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" s="6"/>
+      <c r="D192" s="7"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" s="6"/>
+      <c r="D193" s="7"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" s="6"/>
+      <c r="D194" s="7"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" s="6"/>
+      <c r="D195" s="7"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" s="6"/>
+      <c r="D196" s="7"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="6"/>
+      <c r="D197" s="7"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" s="6"/>
+      <c r="D198" s="7"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="6"/>
+      <c r="D199" s="7"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="6"/>
+      <c r="D200" s="7"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="6"/>
+      <c r="D201" s="7"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="6"/>
+      <c r="D202" s="7"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" s="6"/>
+      <c r="D203" s="7"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" s="6"/>
+      <c r="D204" s="7"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" s="6"/>
+      <c r="D205" s="7"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206" s="6"/>
+      <c r="D206" s="7"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207" s="6"/>
+      <c r="D207" s="7"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A208" s="6"/>
+      <c r="D208" s="7"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A209" s="6"/>
+      <c r="D209" s="7"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A210" s="6"/>
+      <c r="D210" s="7"/>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A211" s="6"/>
+      <c r="D211" s="7"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A212" s="6"/>
+      <c r="D212" s="7"/>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A213" s="6"/>
+      <c r="D213" s="7"/>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A214" s="6"/>
+      <c r="D214" s="7"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A215" s="6"/>
+      <c r="D215" s="7"/>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A216" s="6"/>
+      <c r="D216" s="7"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A217" s="6"/>
+      <c r="D217" s="7"/>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A218" s="6"/>
+      <c r="D218" s="7"/>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A219" s="6"/>
+      <c r="D219" s="7"/>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A220" s="6"/>
+      <c r="D220" s="7"/>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A221" s="6"/>
+      <c r="D221" s="7"/>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222" s="6"/>
+      <c r="D222" s="7"/>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" s="6"/>
+      <c r="D223" s="7"/>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" s="6"/>
+      <c r="D224" s="7"/>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" s="6"/>
+      <c r="D225" s="7"/>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226" s="6"/>
+      <c r="D226" s="7"/>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A227" s="6"/>
+      <c r="D227" s="7"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A228" s="6"/>
+      <c r="D228" s="7"/>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A229" s="6"/>
+      <c r="D229" s="7"/>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A230" s="6"/>
+      <c r="D230" s="7"/>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A231" s="6"/>
+      <c r="D231" s="7"/>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A232" s="6"/>
+      <c r="D232" s="7"/>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A233" s="6"/>
+      <c r="D233" s="7"/>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A234" s="6"/>
+      <c r="D234" s="7"/>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A235" s="6"/>
+      <c r="D235" s="7"/>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A236" s="6"/>
+      <c r="D236" s="7"/>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A237" s="6"/>
+      <c r="D237" s="7"/>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A238" s="6"/>
+      <c r="D238" s="7"/>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A239" s="6"/>
+      <c r="D239" s="7"/>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A240" s="6"/>
+      <c r="D240" s="7"/>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A241" s="6"/>
+      <c r="D241" s="7"/>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242" s="6"/>
+      <c r="D242" s="7"/>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243" s="6"/>
+      <c r="D243" s="7"/>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244" s="6"/>
+      <c r="D244" s="7"/>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" s="6"/>
+      <c r="D245" s="7"/>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" s="6"/>
+      <c r="D246" s="7"/>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" s="6"/>
+      <c r="D247" s="7"/>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" s="6"/>
+      <c r="D248" s="7"/>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" s="6"/>
+      <c r="D249" s="7"/>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" s="6"/>
+      <c r="D250" s="7"/>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A251" s="6"/>
+      <c r="D251" s="7"/>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252" s="6"/>
+      <c r="D252" s="7"/>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253" s="6"/>
+      <c r="D253" s="7"/>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A254" s="6"/>
+      <c r="D254" s="7"/>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A255" s="6"/>
+      <c r="D255" s="7"/>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A256" s="6"/>
+      <c r="D256" s="7"/>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A257" s="6"/>
+      <c r="D257" s="7"/>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A258" s="6"/>
+      <c r="D258" s="7"/>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A259" s="6"/>
+      <c r="D259" s="7"/>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A260" s="6"/>
+      <c r="D260" s="7"/>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A261" s="6"/>
+      <c r="D261" s="7"/>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A262" s="6"/>
+      <c r="D262" s="7"/>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A263" s="6"/>
+      <c r="D263" s="7"/>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A264" s="6"/>
+      <c r="D264" s="7"/>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A265" s="6"/>
+      <c r="D265" s="7"/>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A266" s="6"/>
+      <c r="D266" s="7"/>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A267" s="6"/>
+      <c r="D267" s="7"/>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A268" s="6"/>
+      <c r="D268" s="7"/>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A269" s="6"/>
+      <c r="D269" s="7"/>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A270" s="6"/>
+      <c r="D270" s="7"/>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A271" s="6"/>
+      <c r="D271" s="7"/>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A272" s="6"/>
+      <c r="D272" s="7"/>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A273" s="6"/>
+      <c r="D273" s="7"/>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A274" s="6"/>
+      <c r="D274" s="7"/>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A275" s="6"/>
+      <c r="D275" s="7"/>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A276" s="6"/>
+      <c r="D276" s="7"/>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A277" s="6"/>
+      <c r="D277" s="7"/>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A278" s="6"/>
+      <c r="D278" s="7"/>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A279" s="6"/>
+      <c r="D279" s="7"/>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A280" s="6"/>
+      <c r="D280" s="7"/>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A281" s="6"/>
+      <c r="D281" s="7"/>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A282" s="6"/>
+      <c r="D282" s="7"/>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A283" s="6"/>
+      <c r="D283" s="7"/>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A284" s="6"/>
+      <c r="D284" s="7"/>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A285" s="6"/>
+      <c r="D285" s="7"/>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A286" s="6"/>
+      <c r="D286" s="7"/>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A287" s="6"/>
+      <c r="D287" s="7"/>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A288" s="6"/>
+      <c r="D288" s="7"/>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A289" s="6"/>
+      <c r="D289" s="7"/>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A290" s="6"/>
+      <c r="D290" s="7"/>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A291" s="6"/>
+      <c r="D291" s="7"/>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A292" s="6"/>
+      <c r="D292" s="7"/>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A293" s="6"/>
+      <c r="D293" s="7"/>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A294" s="6"/>
+      <c r="D294" s="7"/>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A295" s="6"/>
+      <c r="D295" s="7"/>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A296" s="6"/>
+      <c r="D296" s="7"/>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A297" s="6"/>
+      <c r="D297" s="7"/>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A298" s="6"/>
+      <c r="D298" s="7"/>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A299" s="6"/>
+      <c r="D299" s="7"/>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A300" s="6"/>
+      <c r="D300" s="7"/>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A301" s="6"/>
+      <c r="D301" s="7"/>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A302" s="6"/>
+      <c r="D302" s="7"/>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A303" s="6"/>
+      <c r="D303" s="7"/>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A304" s="6"/>
+      <c r="D304" s="7"/>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A305" s="6"/>
+      <c r="D305" s="7"/>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A306" s="6"/>
+      <c r="D306" s="7"/>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A307" s="6"/>
+      <c r="D307" s="7"/>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A308" s="6"/>
+      <c r="D308" s="7"/>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A309" s="6"/>
+      <c r="D309" s="7"/>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A310" s="6"/>
+      <c r="D310" s="7"/>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A311" s="6"/>
+      <c r="D311" s="7"/>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A312" s="6"/>
+      <c r="D312" s="7"/>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A313" s="6"/>
+      <c r="D313" s="7"/>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A314" s="6"/>
+      <c r="D314" s="7"/>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A315" s="6"/>
+      <c r="D315" s="7"/>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A316" s="6"/>
+      <c r="D316" s="7"/>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A317" s="6"/>
+      <c r="D317" s="7"/>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A318" s="6"/>
+      <c r="D318" s="7"/>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A319" s="6"/>
+      <c r="D319" s="7"/>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A320" s="6"/>
+      <c r="D320" s="7"/>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A321" s="6"/>
+      <c r="D321" s="7"/>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A322" s="6"/>
+      <c r="D322" s="7"/>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A323" s="6"/>
+      <c r="D323" s="7"/>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A324" s="6"/>
+      <c r="D324" s="7"/>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A325" s="6"/>
+      <c r="D325" s="7"/>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A326" s="6"/>
+      <c r="D326" s="7"/>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A327" s="6"/>
+      <c r="D327" s="7"/>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A328" s="6"/>
+      <c r="D328" s="7"/>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A329" s="6"/>
+      <c r="D329" s="7"/>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A330" s="6"/>
+      <c r="D330" s="7"/>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A331" s="6"/>
+      <c r="D331" s="7"/>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A332" s="6"/>
+      <c r="D332" s="7"/>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A333" s="6"/>
+      <c r="D333" s="7"/>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A334" s="6"/>
+      <c r="D334" s="7"/>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A335" s="6"/>
+      <c r="D335" s="7"/>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A336" s="6"/>
+      <c r="D336" s="7"/>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A337" s="6"/>
+      <c r="D337" s="7"/>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A338" s="6"/>
+      <c r="D338" s="7"/>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A339" s="6"/>
+      <c r="D339" s="7"/>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A340" s="6"/>
+      <c r="D340" s="7"/>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A341" s="6"/>
+      <c r="D341" s="7"/>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A342" s="6"/>
+      <c r="D342" s="7"/>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A343" s="6"/>
+      <c r="D343" s="7"/>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A344" s="6"/>
+      <c r="D344" s="7"/>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A345" s="6"/>
+      <c r="D345" s="7"/>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A346" s="6"/>
+      <c r="D346" s="7"/>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A347" s="6"/>
+      <c r="D347" s="7"/>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A348" s="6"/>
+      <c r="D348" s="7"/>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A349" s="6"/>
+      <c r="D349" s="7"/>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A350" s="6"/>
+      <c r="D350" s="7"/>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A351" s="6"/>
+      <c r="D351" s="7"/>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A352" s="6"/>
+      <c r="D352" s="7"/>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A353" s="6"/>
+      <c r="D353" s="7"/>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A354" s="6"/>
+      <c r="D354" s="7"/>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A355" s="6"/>
+      <c r="D355" s="7"/>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A356" s="6"/>
+      <c r="D356" s="7"/>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A357" s="6"/>
+      <c r="D357" s="7"/>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A358" s="6"/>
+      <c r="D358" s="7"/>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A359" s="6"/>
+      <c r="D359" s="7"/>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A360" s="6"/>
+      <c r="D360" s="7"/>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A361" s="6"/>
+      <c r="D361" s="7"/>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A362" s="6"/>
+      <c r="D362" s="7"/>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A363" s="6"/>
+      <c r="D363" s="7"/>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A364" s="6"/>
+      <c r="D364" s="7"/>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A365" s="6"/>
+      <c r="D365" s="7"/>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A366" s="6"/>
+      <c r="D366" s="7"/>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A367" s="6"/>
+      <c r="D367" s="7"/>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A368" s="6"/>
+      <c r="D368" s="7"/>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A369" s="6"/>
+      <c r="D369" s="7"/>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A370" s="6"/>
+      <c r="D370" s="7"/>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A371" s="6"/>
+      <c r="D371" s="7"/>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A372" s="6"/>
+      <c r="D372" s="7"/>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A373" s="6"/>
+      <c r="D373" s="7"/>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A374" s="6"/>
+      <c r="D374" s="7"/>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A375" s="6"/>
+      <c r="D375" s="7"/>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A376" s="6"/>
+      <c r="D376" s="7"/>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A377" s="6"/>
+      <c r="D377" s="7"/>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A378" s="6"/>
+      <c r="D378" s="7"/>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A379" s="6"/>
+      <c r="D379" s="7"/>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A380" s="6"/>
+      <c r="D380" s="7"/>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A381" s="6"/>
+      <c r="D381" s="7"/>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A382" s="6"/>
+      <c r="D382" s="7"/>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A383" s="6"/>
+      <c r="D383" s="7"/>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A384" s="6"/>
+      <c r="D384" s="7"/>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A385" s="6"/>
+      <c r="D385" s="7"/>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A386" s="6"/>
+      <c r="D386" s="7"/>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A387" s="6"/>
+      <c r="D387" s="7"/>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A388" s="6"/>
+      <c r="D388" s="7"/>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A389" s="6"/>
+      <c r="D389" s="7"/>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A390" s="6"/>
+      <c r="D390" s="7"/>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A391" s="6"/>
+      <c r="D391" s="7"/>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A392" s="6"/>
+      <c r="D392" s="7"/>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A393" s="6"/>
+      <c r="D393" s="7"/>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A394" s="6"/>
+      <c r="D394" s="7"/>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A395" s="6"/>
+      <c r="D395" s="7"/>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A396" s="6"/>
+      <c r="D396" s="7"/>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A397" s="6"/>
+      <c r="D397" s="7"/>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A398" s="6"/>
+      <c r="D398" s="7"/>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A399" s="6"/>
+      <c r="D399" s="7"/>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A400" s="6"/>
+      <c r="D400" s="7"/>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A401" s="6"/>
+      <c r="D401" s="7"/>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A402" s="6"/>
+      <c r="D402" s="7"/>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A403" s="6"/>
+      <c r="D403" s="7"/>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A404" s="6"/>
+      <c r="D404" s="7"/>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A405" s="6"/>
+      <c r="D405" s="7"/>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A406" s="6"/>
+      <c r="D406" s="7"/>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A407" s="6"/>
+      <c r="D407" s="7"/>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A408" s="6"/>
+      <c r="D408" s="7"/>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A409" s="6"/>
+      <c r="D409" s="7"/>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A410" s="6"/>
+      <c r="D410" s="7"/>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A411" s="6"/>
+      <c r="D411" s="7"/>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A412" s="6"/>
+      <c r="D412" s="7"/>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A413" s="6"/>
+      <c r="D413" s="7"/>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A414" s="6"/>
+      <c r="D414" s="7"/>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A415" s="6"/>
+      <c r="D415" s="7"/>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A416" s="6"/>
+      <c r="D416" s="7"/>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A417" s="6"/>
+      <c r="D417" s="7"/>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A418" s="6"/>
+      <c r="D418" s="7"/>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A419" s="6"/>
+      <c r="D419" s="7"/>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A420" s="6"/>
+      <c r="D420" s="7"/>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A421" s="6"/>
+      <c r="D421" s="7"/>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A422" s="6"/>
+      <c r="D422" s="7"/>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A423" s="6"/>
+      <c r="D423" s="7"/>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A424" s="6"/>
+      <c r="D424" s="7"/>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A425" s="6"/>
+      <c r="D425" s="7"/>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A426" s="6"/>
+      <c r="D426" s="7"/>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A427" s="6"/>
+      <c r="D427" s="7"/>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A428" s="6"/>
+      <c r="D428" s="7"/>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A429" s="6"/>
+      <c r="D429" s="7"/>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A430" s="6"/>
+      <c r="D430" s="7"/>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A431" s="6"/>
+      <c r="D431" s="7"/>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A432" s="6"/>
+      <c r="D432" s="7"/>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A433" s="6"/>
+      <c r="D433" s="7"/>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A434" s="6"/>
+      <c r="D434" s="7"/>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A435" s="6"/>
+      <c r="D435" s="7"/>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A436" s="6"/>
+      <c r="D436" s="7"/>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A437" s="6"/>
+      <c r="D437" s="7"/>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A438" s="6"/>
+      <c r="D438" s="7"/>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A439" s="6"/>
+      <c r="D439" s="7"/>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A440" s="6"/>
+      <c r="D440" s="7"/>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A441" s="6"/>
+      <c r="D441" s="7"/>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A442" s="6"/>
+      <c r="D442" s="7"/>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A443" s="6"/>
+      <c r="D443" s="7"/>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A444" s="6"/>
+      <c r="D444" s="7"/>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A445" s="6"/>
+      <c r="D445" s="7"/>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A446" s="6"/>
+      <c r="D446" s="7"/>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A447" s="6"/>
+      <c r="D447" s="7"/>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A448" s="6"/>
+      <c r="D448" s="7"/>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A449" s="6"/>
+      <c r="D449" s="7"/>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A450" s="6"/>
+      <c r="D450" s="7"/>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A451" s="6"/>
+      <c r="D451" s="7"/>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A452" s="6"/>
+      <c r="D452" s="7"/>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A453" s="6"/>
+      <c r="D453" s="7"/>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A454" s="6"/>
+      <c r="D454" s="7"/>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A455" s="6"/>
+      <c r="D455" s="7"/>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A456" s="6"/>
+      <c r="D456" s="7"/>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A457" s="6"/>
+      <c r="D457" s="7"/>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A458" s="6"/>
+      <c r="D458" s="7"/>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A459" s="6"/>
+      <c r="D459" s="7"/>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A460" s="6"/>
+      <c r="D460" s="7"/>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A461" s="6"/>
+      <c r="D461" s="7"/>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A462" s="6"/>
+      <c r="D462" s="7"/>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A463" s="6"/>
+      <c r="D463" s="7"/>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A464" s="6"/>
+      <c r="D464" s="7"/>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A465" s="6"/>
+      <c r="D465" s="7"/>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A466" s="6"/>
+      <c r="D466" s="7"/>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A467" s="6"/>
+      <c r="D467" s="7"/>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A468" s="6"/>
+      <c r="D468" s="7"/>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A469" s="6"/>
+      <c r="D469" s="7"/>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A470" s="6"/>
+      <c r="D470" s="7"/>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A471" s="6"/>
+      <c r="D471" s="7"/>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A472" s="6"/>
+      <c r="D472" s="7"/>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A473" s="6"/>
+      <c r="D473" s="7"/>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A474" s="6"/>
+      <c r="D474" s="7"/>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A475" s="6"/>
+      <c r="D475" s="7"/>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A476" s="6"/>
+      <c r="D476" s="7"/>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A477" s="6"/>
+      <c r="D477" s="7"/>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A478" s="6"/>
+      <c r="D478" s="7"/>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A479" s="6"/>
+      <c r="D479" s="7"/>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A480" s="6"/>
+      <c r="D480" s="7"/>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A481" s="6"/>
+      <c r="D481" s="7"/>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A482" s="6"/>
+      <c r="D482" s="7"/>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A483" s="6"/>
+      <c r="D483" s="7"/>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A484" s="6"/>
+      <c r="D484" s="7"/>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A485" s="6"/>
+      <c r="D485" s="7"/>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A486" s="6"/>
+      <c r="D486" s="7"/>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A487" s="6"/>
+      <c r="D487" s="7"/>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A488" s="6"/>
+      <c r="D488" s="7"/>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A489" s="6"/>
+      <c r="D489" s="7"/>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A490" s="6"/>
+      <c r="D490" s="7"/>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A491" s="6"/>
+      <c r="D491" s="7"/>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A492" s="6"/>
+      <c r="D492" s="7"/>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A493" s="6"/>
+      <c r="D493" s="7"/>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A494" s="6"/>
+      <c r="D494" s="7"/>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A495" s="6"/>
+      <c r="D495" s="7"/>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A496" s="6"/>
+      <c r="D496" s="7"/>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A497" s="6"/>
+      <c r="D497" s="7"/>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A498" s="6"/>
+      <c r="D498" s="7"/>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A499" s="6"/>
+      <c r="D499" s="7"/>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A500" s="6"/>
+      <c r="D500" s="7"/>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A501" s="6"/>
+      <c r="D501" s="7"/>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A502" s="6"/>
+      <c r="D502" s="7"/>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A503" s="6"/>
+      <c r="D503" s="7"/>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A504" s="6"/>
+      <c r="D504" s="7"/>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A505" s="6"/>
+      <c r="D505" s="7"/>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A506" s="6"/>
+      <c r="D506" s="7"/>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A507" s="6"/>
+      <c r="D507" s="7"/>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A508" s="6"/>
+      <c r="D508" s="7"/>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A509" s="6"/>
+      <c r="D509" s="7"/>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A510" s="6"/>
+      <c r="D510" s="7"/>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A511" s="6"/>
+      <c r="D511" s="7"/>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A512" s="6"/>
+      <c r="D512" s="7"/>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A513" s="6"/>
+      <c r="D513" s="7"/>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A514" s="6"/>
+      <c r="D514" s="7"/>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A515" s="6"/>
+      <c r="D515" s="7"/>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A516" s="6"/>
+      <c r="D516" s="7"/>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A517" s="6"/>
+      <c r="D517" s="7"/>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A518" s="6"/>
+      <c r="D518" s="7"/>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A519" s="6"/>
+      <c r="D519" s="7"/>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A520" s="6"/>
+      <c r="D520" s="7"/>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A521" s="6"/>
+      <c r="D521" s="7"/>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A522" s="6"/>
+      <c r="D522" s="7"/>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A523" s="6"/>
+      <c r="D523" s="7"/>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A524" s="6"/>
+      <c r="D524" s="7"/>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A525" s="6"/>
+      <c r="D525" s="7"/>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A526" s="6"/>
+      <c r="D526" s="7"/>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A527" s="6"/>
+      <c r="D527" s="7"/>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A528" s="6"/>
+      <c r="D528" s="7"/>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A529" s="6"/>
+      <c r="D529" s="7"/>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A530" s="6"/>
+      <c r="D530" s="7"/>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A531" s="6"/>
+      <c r="D531" s="7"/>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A532" s="6"/>
+      <c r="D532" s="7"/>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A533" s="6"/>
+      <c r="D533" s="7"/>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A534" s="6"/>
+      <c r="D534" s="7"/>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A535" s="6"/>
+      <c r="D535" s="7"/>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A536" s="6"/>
+      <c r="D536" s="7"/>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A537" s="6"/>
+      <c r="D537" s="7"/>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A538" s="6"/>
+      <c r="D538" s="7"/>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A539" s="6"/>
+      <c r="D539" s="7"/>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A540" s="6"/>
+      <c r="D540" s="7"/>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A541" s="6"/>
+      <c r="D541" s="7"/>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A542" s="6"/>
+      <c r="D542" s="7"/>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A543" s="6"/>
+      <c r="D543" s="7"/>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A544" s="6"/>
+      <c r="D544" s="7"/>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A545" s="6"/>
+      <c r="D545" s="7"/>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A546" s="6"/>
+      <c r="D546" s="7"/>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A547" s="6"/>
+      <c r="D547" s="7"/>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A548" s="6"/>
+      <c r="D548" s="7"/>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A549" s="6"/>
+      <c r="D549" s="7"/>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A550" s="6"/>
+      <c r="D550" s="7"/>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A551" s="6"/>
+      <c r="D551" s="7"/>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A552" s="6"/>
+      <c r="D552" s="7"/>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A553" s="6"/>
+      <c r="D553" s="7"/>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A554" s="6"/>
+      <c r="D554" s="7"/>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A555" s="6"/>
+      <c r="D555" s="7"/>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A556" s="6"/>
+      <c r="D556" s="7"/>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A557" s="6"/>
+      <c r="D557" s="7"/>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A558" s="6"/>
+      <c r="D558" s="7"/>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A559" s="6"/>
+      <c r="D559" s="7"/>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A560" s="6"/>
+      <c r="D560" s="7"/>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A561" s="6"/>
+      <c r="D561" s="7"/>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A562" s="6"/>
+      <c r="D562" s="7"/>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A563" s="6"/>
+      <c r="D563" s="7"/>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A564" s="6"/>
+      <c r="D564" s="7"/>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A565" s="6"/>
+      <c r="D565" s="7"/>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A566" s="6"/>
+      <c r="D566" s="7"/>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A567" s="6"/>
+      <c r="D567" s="7"/>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A568" s="6"/>
+      <c r="D568" s="7"/>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A569" s="6"/>
+      <c r="D569" s="7"/>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A570" s="6"/>
+      <c r="D570" s="7"/>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A571" s="6"/>
+      <c r="D571" s="7"/>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A572" s="6"/>
+      <c r="D572" s="7"/>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A573" s="6"/>
+      <c r="D573" s="7"/>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A574" s="6"/>
+      <c r="D574" s="7"/>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A575" s="6"/>
+      <c r="D575" s="7"/>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A576" s="6"/>
+      <c r="D576" s="7"/>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A577" s="6"/>
+      <c r="D577" s="7"/>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A578" s="6"/>
+      <c r="D578" s="7"/>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A579" s="6"/>
+      <c r="D579" s="7"/>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A580" s="6"/>
+      <c r="D580" s="7"/>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A581" s="6"/>
+      <c r="D581" s="7"/>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A582" s="6"/>
+      <c r="D582" s="7"/>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A583" s="6"/>
+      <c r="D583" s="7"/>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A584" s="6"/>
+      <c r="D584" s="7"/>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A585" s="6"/>
+      <c r="D585" s="7"/>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A586" s="6"/>
+      <c r="D586" s="7"/>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A587" s="6"/>
+      <c r="D587" s="7"/>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A588" s="6"/>
+      <c r="D588" s="7"/>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A589" s="6"/>
+      <c r="D589" s="7"/>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A590" s="6"/>
+      <c r="D590" s="7"/>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A591" s="6"/>
+      <c r="D591" s="7"/>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A592" s="6"/>
+      <c r="D592" s="7"/>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A593" s="6"/>
+      <c r="D593" s="7"/>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A594" s="6"/>
+      <c r="D594" s="7"/>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A595" s="6"/>
+      <c r="D595" s="7"/>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A596" s="6"/>
+      <c r="D596" s="7"/>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A597" s="6"/>
+      <c r="D597" s="7"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D147">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Cần bổ sung">
+      <formula>NOT(ISERROR(SEARCH("Cần bổ sung",D2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>